--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0040.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0040.xlsx
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Không biết có ai ở đây muốn mua chúng không, giống như chú Trần Tì ở Kim Châu ấy.</t>
+          <t>Không biết có ai ở đây muốn mua chúng không, giống như chú Trần Tì ở Jinzhou ấy.</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Tuyệt vời! Giờ ta đang cần một vị cứu tinh đây.</t>
+          <t>Tuyệt vời! Giờ tao đang cần một vị cứu tinh đây.</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Có gì cho tôi không?</t>
+          <t>Giúp thì được gì chứ?</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Ta đã cố nhìn sâu vào mạng lưới để xem có gì ở phía bên kia. Chỉ thoáng qua, ta thấy một khung hình duy nhất và suýt chìm trong âm thanh cuồn cuộn, lạc mất chính mình.</t>
+          <t>Tao đã cố nhìn sâu vào mạng lưới để xem có gì ở phía bên kia. Chỉ thoáng qua, tao thấy một khung hình duy nhất và suýt chìm trong âm thanh cuồn cuộn, lạc mất chính mình.</t>
         </is>
       </c>
     </row>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Hồi còn lo lắng quá mức, ta đã tích trữ hết mớ đồ này, nhưng giờ ta không cần nữa rồi.</t>
+          <t>Hồi còn lo lắng quá mức, tao đã tích trữ hết mớ đồ này, nhưng giờ tao không cần nữa rồi.</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Nghe này nghe nè! Chúng ta đang lên kế hoạch đặt làm một &lt;color=Highlight&gt;statue&lt;/color&gt; để vinh danh cậu, và sẽ đặt ngay tại đây!</t>
+          <t>Nghe này nghe nè! Chúng ta đang lên kế hoạch đặt làm một &lt;color=Highlight&gt;bức tượng&lt;/color&gt; để vinh danh cậu, và sẽ đặt ngay tại đây!</t>
         </is>
       </c>
     </row>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Được rồi, tôi đã nắm được rồi! Chúng ta sẽ gửi nó cho nhà điêu khắc. Quay lại sau vài ngày, và cậu sẽ thấy &lt;color=Highlight&gt;exclusive statue&lt;/color&gt; của mình!</t>
+          <t>Được rồi, tôi đã nắm được rồi! Chúng ta sẽ gửi nó cho nhà điêu khắc. Quay lại sau vài ngày, và cậu sẽ thấy &lt;color=Highlight&gt;bức tượng độc quyền&lt;/color&gt; của mình!</t>
         </is>
       </c>
     </row>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Sau khi hòn đá đến nơi, ta lo sợ có kẻ sẽ đánh cắp nó, nên ở lại đây và nhờ Fratello mang bức chân dung của cậu đến cho thợ điêu khắc.</t>
+          <t>Sau khi hòn đá đến nơi, tao lo sợ có kẻ sẽ đánh cắp nó, nên ở lại đây và nhờ Fratello mang bức chân dung của cậu đến cho thợ điêu khắc.</t>
         </is>
       </c>
     </row>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Cậu còn đang tập luyện à?</t>
+          <t>Mày còn đang tập luyện à?</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Lúc đầu, chỉ là linh cảm thôi, nhưng càng đào sâu vào những tài liệu không chính thức này, ta càng thấy nghi ngờ.</t>
+          <t>Lúc đầu, chỉ là linh cảm thôi, nhưng càng đào sâu vào những tài liệu không chính thức này, tao càng thấy nghi ngờ.</t>
         </is>
       </c>
     </row>
